--- a/backend-excel/data/matches.xlsx
+++ b/backend-excel/data/matches.xlsx
@@ -401,43 +401,43 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>id</v>
+        <v>ID</v>
       </c>
       <c r="B1" t="str">
-        <v>groupKey</v>
+        <v>GROUPKEY</v>
       </c>
       <c r="C1" t="str">
-        <v>round</v>
+        <v>ROUND</v>
       </c>
       <c r="D1" t="str">
-        <v>time</v>
+        <v>TIME</v>
       </c>
       <c r="E1" t="str">
-        <v>homeTeamName</v>
+        <v>HOMETEAMNAME</v>
       </c>
       <c r="F1" t="str">
-        <v>homeTeamFlag</v>
+        <v>HOMETEAMFLAG</v>
       </c>
       <c r="G1" t="str">
-        <v>awayTeamName</v>
+        <v>AWAYTEAMNAME</v>
       </c>
       <c r="H1" t="str">
-        <v>awayTeamFlag</v>
+        <v>AWAYTEAMFLAG</v>
       </c>
       <c r="I1" t="str">
-        <v>status</v>
+        <v>STATUS</v>
       </c>
       <c r="J1" t="str">
-        <v>homeTeamGoals</v>
+        <v>HOMETEAMGOALS</v>
       </c>
       <c r="K1" t="str">
-        <v>awayTeamGoals</v>
+        <v>AWAYTEAMGOALS</v>
       </c>
       <c r="L1" t="str">
-        <v>elapsedMinutes</v>
+        <v>ELAPSEDMINUTES</v>
       </c>
       <c r="M1" t="str">
-        <v>stadium</v>
+        <v>STADIUM</v>
       </c>
     </row>
     <row r="2">

--- a/backend-excel/data/matches.xlsx
+++ b/backend-excel/data/matches.xlsx
@@ -4668,7 +4668,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>final</v>
+        <v>knockout</v>
       </c>
       <c r="C105" t="str">
         <v>Chung Kết</v>

--- a/backend-excel/data/matches.xlsx
+++ b/backend-excel/data/matches.xlsx
@@ -4668,7 +4668,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>knockout</v>
+        <v>final</v>
       </c>
       <c r="C105" t="str">
         <v>Chung Kết</v>

--- a/backend-excel/data/matches.xlsx
+++ b/backend-excel/data/matches.xlsx
@@ -466,13 +466,13 @@
         <v>🇿🇦</v>
       </c>
       <c r="I2" t="str">
-        <v>scheduled</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
+        <v>completed</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -507,13 +507,13 @@
         <v>🇨🇿</v>
       </c>
       <c r="I3" t="str">
-        <v>scheduled</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
+        <v>completed</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
       </c>
       <c r="L3" t="str">
         <v/>

--- a/backend-excel/data/matches.xlsx
+++ b/backend-excel/data/matches.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M105"/>
+  <dimension ref="A1:S105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,6 +439,24 @@
       <c r="M1" t="str">
         <v>STADIUM</v>
       </c>
+      <c r="N1" t="str">
+        <v>HOMEGOALS90</v>
+      </c>
+      <c r="O1" t="str">
+        <v>AWAYGOALS90</v>
+      </c>
+      <c r="P1" t="str">
+        <v>EXTRAHOMEGOALS</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>EXTRAAWAYGOALS</v>
+      </c>
+      <c r="R1" t="str">
+        <v>PENHOMEGOALS</v>
+      </c>
+      <c r="S1" t="str">
+        <v>PENAWAYGOALS</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -480,6 +498,24 @@
       <c r="M2" t="str">
         <v>Estadio Azteca</v>
       </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -521,6 +557,24 @@
       <c r="M3" t="str">
         <v>Estadio Akron</v>
       </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -562,6 +616,24 @@
       <c r="M4" t="str">
         <v>BMO Field</v>
       </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -603,6 +675,24 @@
       <c r="M5" t="str">
         <v>SoFi Stadium</v>
       </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -644,6 +734,24 @@
       <c r="M6" t="str">
         <v>Levi's Stadium</v>
       </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -685,6 +793,24 @@
       <c r="M7" t="str">
         <v>MetLife Stadium</v>
       </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -726,6 +852,24 @@
       <c r="M8" t="str">
         <v>Gillette Stadium</v>
       </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -767,6 +911,24 @@
       <c r="M9" t="str">
         <v>BC Place</v>
       </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -808,6 +970,24 @@
       <c r="M10" t="str">
         <v>NRG Stadium</v>
       </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -849,6 +1029,24 @@
       <c r="M11" t="str">
         <v>AT&amp;T Stadium</v>
       </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -890,6 +1088,24 @@
       <c r="M12" t="str">
         <v>Lincoln Financial Field</v>
       </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -931,6 +1147,24 @@
       <c r="M13" t="str">
         <v>Estadio BBVA</v>
       </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -972,6 +1206,24 @@
       <c r="M14" t="str">
         <v>Mercedes-Benz Stadium</v>
       </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -1013,6 +1265,24 @@
       <c r="M15" t="str">
         <v>Lumen Field</v>
       </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -1054,6 +1324,24 @@
       <c r="M16" t="str">
         <v>Hard Rock Stadium</v>
       </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -1095,6 +1383,24 @@
       <c r="M17" t="str">
         <v>SoFi Stadium</v>
       </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1136,6 +1442,24 @@
       <c r="M18" t="str">
         <v>MetLife Stadium</v>
       </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -1177,6 +1501,24 @@
       <c r="M19" t="str">
         <v>Gillette Stadium</v>
       </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1218,6 +1560,24 @@
       <c r="M20" t="str">
         <v>GEHA Field at Arrowhead Stadium</v>
       </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -1259,6 +1619,24 @@
       <c r="M21" t="str">
         <v>Levi's Stadium</v>
       </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -1300,6 +1678,24 @@
       <c r="M22" t="str">
         <v>NRG Stadium</v>
       </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -1341,6 +1737,24 @@
       <c r="M23" t="str">
         <v>AT&amp;T Stadium</v>
       </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -1382,6 +1796,24 @@
       <c r="M24" t="str">
         <v>BMO Field</v>
       </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -1423,6 +1855,24 @@
       <c r="M25" t="str">
         <v>Estadio Azteca</v>
       </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -1464,6 +1914,24 @@
       <c r="M26" t="str">
         <v>Mercedes-Benz Stadium</v>
       </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -1505,6 +1973,24 @@
       <c r="M27" t="str">
         <v>SoFi Stadium</v>
       </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -1546,6 +2032,24 @@
       <c r="M28" t="str">
         <v>BC Place</v>
       </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -1587,6 +2091,24 @@
       <c r="M29" t="str">
         <v>Estadio Akron</v>
       </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <v/>
+      </c>
+      <c r="S29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1628,6 +2150,24 @@
       <c r="M30" t="str">
         <v>Lumen Field</v>
       </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1669,6 +2209,24 @@
       <c r="M31" t="str">
         <v>Gillette Stadium</v>
       </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
+        <v/>
+      </c>
+      <c r="S31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -1710,6 +2268,24 @@
       <c r="M32" t="str">
         <v>Lincoln Financial Field</v>
       </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
+        <v/>
+      </c>
+      <c r="R32" t="str">
+        <v/>
+      </c>
+      <c r="S32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -1751,6 +2327,24 @@
       <c r="M33" t="str">
         <v>Levi's Stadium</v>
       </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
+        <v/>
+      </c>
+      <c r="R33" t="str">
+        <v/>
+      </c>
+      <c r="S33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1792,6 +2386,24 @@
       <c r="M34" t="str">
         <v>NRG Stadium</v>
       </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
+        <v/>
+      </c>
+      <c r="R34" t="str">
+        <v/>
+      </c>
+      <c r="S34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -1833,6 +2445,24 @@
       <c r="M35" t="str">
         <v>BMO Field</v>
       </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
+        <v/>
+      </c>
+      <c r="R35" t="str">
+        <v/>
+      </c>
+      <c r="S35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1874,6 +2504,24 @@
       <c r="M36" t="str">
         <v>GEHA Field at Arrowhead Stadium</v>
       </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
+      <c r="R36" t="str">
+        <v/>
+      </c>
+      <c r="S36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -1915,6 +2563,24 @@
       <c r="M37" t="str">
         <v>Estadio BBVA</v>
       </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
+      <c r="R37" t="str">
+        <v/>
+      </c>
+      <c r="S37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -1956,6 +2622,24 @@
       <c r="M38" t="str">
         <v>Mercedes-Benz Stadium</v>
       </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
+        <v/>
+      </c>
+      <c r="R38" t="str">
+        <v/>
+      </c>
+      <c r="S38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -1997,6 +2681,24 @@
       <c r="M39" t="str">
         <v>SoFi Stadium</v>
       </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
+      <c r="R39" t="str">
+        <v/>
+      </c>
+      <c r="S39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -2038,6 +2740,24 @@
       <c r="M40" t="str">
         <v>Hard Rock Stadium</v>
       </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
+      <c r="R40" t="str">
+        <v/>
+      </c>
+      <c r="S40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -2079,6 +2799,24 @@
       <c r="M41" t="str">
         <v>BC Place</v>
       </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
+      <c r="R41" t="str">
+        <v/>
+      </c>
+      <c r="S41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -2120,6 +2858,24 @@
       <c r="M42" t="str">
         <v>AT&amp;T Stadium</v>
       </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
+        <v/>
+      </c>
+      <c r="R42" t="str">
+        <v/>
+      </c>
+      <c r="S42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -2161,6 +2917,24 @@
       <c r="M43" t="str">
         <v>Lincoln Financial Field</v>
       </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
+      <c r="R43" t="str">
+        <v/>
+      </c>
+      <c r="S43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -2202,6 +2976,24 @@
       <c r="M44" t="str">
         <v>MetLife Stadium</v>
       </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
+      <c r="R44" t="str">
+        <v/>
+      </c>
+      <c r="S44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -2243,6 +3035,24 @@
       <c r="M45" t="str">
         <v>Levi's Stadium</v>
       </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+      <c r="Q45" t="str">
+        <v/>
+      </c>
+      <c r="R45" t="str">
+        <v/>
+      </c>
+      <c r="S45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -2284,6 +3094,24 @@
       <c r="M46" t="str">
         <v>NRG Stadium</v>
       </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
+      <c r="R46" t="str">
+        <v/>
+      </c>
+      <c r="S46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -2325,6 +3153,24 @@
       <c r="M47" t="str">
         <v>Gillette Stadium</v>
       </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+      <c r="Q47" t="str">
+        <v/>
+      </c>
+      <c r="R47" t="str">
+        <v/>
+      </c>
+      <c r="S47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -2366,6 +3212,24 @@
       <c r="M48" t="str">
         <v>BMO Field</v>
       </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
+      <c r="R48" t="str">
+        <v/>
+      </c>
+      <c r="S48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -2407,6 +3271,24 @@
       <c r="M49" t="str">
         <v>Estadio Akron</v>
       </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
+      <c r="R49" t="str">
+        <v/>
+      </c>
+      <c r="S49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -2448,6 +3330,24 @@
       <c r="M50" t="str">
         <v>Lumen Field</v>
       </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
+      <c r="R50" t="str">
+        <v/>
+      </c>
+      <c r="S50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -2489,6 +3389,24 @@
       <c r="M51" t="str">
         <v>BC Place</v>
       </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
+      <c r="R51" t="str">
+        <v/>
+      </c>
+      <c r="S51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -2530,6 +3448,24 @@
       <c r="M52" t="str">
         <v>Hard Rock Stadium</v>
       </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+      <c r="Q52" t="str">
+        <v/>
+      </c>
+      <c r="R52" t="str">
+        <v/>
+      </c>
+      <c r="S52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -2571,6 +3507,24 @@
       <c r="M53" t="str">
         <v>Mercedes-Benz Stadium</v>
       </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
+      <c r="R53" t="str">
+        <v/>
+      </c>
+      <c r="S53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -2612,6 +3566,24 @@
       <c r="M54" t="str">
         <v>Estadio BBVA</v>
       </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
+      <c r="R54" t="str">
+        <v/>
+      </c>
+      <c r="S54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -2653,6 +3625,24 @@
       <c r="M55" t="str">
         <v>Estadio Azteca</v>
       </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+      <c r="Q55" t="str">
+        <v/>
+      </c>
+      <c r="R55" t="str">
+        <v/>
+      </c>
+      <c r="S55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -2694,6 +3684,24 @@
       <c r="M56" t="str">
         <v>Lincoln Financial Field</v>
       </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+      <c r="Q56" t="str">
+        <v/>
+      </c>
+      <c r="R56" t="str">
+        <v/>
+      </c>
+      <c r="S56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -2735,6 +3743,24 @@
       <c r="M57" t="str">
         <v>MetLife Stadium</v>
       </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+      <c r="Q57" t="str">
+        <v/>
+      </c>
+      <c r="R57" t="str">
+        <v/>
+      </c>
+      <c r="S57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -2776,6 +3802,24 @@
       <c r="M58" t="str">
         <v>AT&amp;T Stadium</v>
       </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+      <c r="Q58" t="str">
+        <v/>
+      </c>
+      <c r="R58" t="str">
+        <v/>
+      </c>
+      <c r="S58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -2817,6 +3861,24 @@
       <c r="M59" t="str">
         <v>GEHA Field at Arrowhead Stadium</v>
       </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+      <c r="Q59" t="str">
+        <v/>
+      </c>
+      <c r="R59" t="str">
+        <v/>
+      </c>
+      <c r="S59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -2858,6 +3920,24 @@
       <c r="M60" t="str">
         <v>Levi's Stadium</v>
       </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+      <c r="Q60" t="str">
+        <v/>
+      </c>
+      <c r="R60" t="str">
+        <v/>
+      </c>
+      <c r="S60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -2899,6 +3979,24 @@
       <c r="M61" t="str">
         <v>SoFi Stadium</v>
       </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61" t="str">
+        <v/>
+      </c>
+      <c r="R61" t="str">
+        <v/>
+      </c>
+      <c r="S61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -2940,6 +4038,24 @@
       <c r="M62" t="str">
         <v>BMO Field</v>
       </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+      <c r="Q62" t="str">
+        <v/>
+      </c>
+      <c r="R62" t="str">
+        <v/>
+      </c>
+      <c r="S62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -2981,6 +4097,24 @@
       <c r="M63" t="str">
         <v>Gillette Stadium</v>
       </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
+      <c r="R63" t="str">
+        <v/>
+      </c>
+      <c r="S63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -3022,6 +4156,24 @@
       <c r="M64" t="str">
         <v>NRG Stadium</v>
       </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
+      <c r="R64" t="str">
+        <v/>
+      </c>
+      <c r="S64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65">
@@ -3063,6 +4215,24 @@
       <c r="M65" t="str">
         <v>Estadio Akron</v>
       </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
+      <c r="R65" t="str">
+        <v/>
+      </c>
+      <c r="S65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66">
@@ -3104,6 +4274,24 @@
       <c r="M66" t="str">
         <v>Lumen Field</v>
       </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
+      <c r="R66" t="str">
+        <v/>
+      </c>
+      <c r="S66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -3145,6 +4333,24 @@
       <c r="M67" t="str">
         <v>BC Place</v>
       </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
+      <c r="R67" t="str">
+        <v/>
+      </c>
+      <c r="S67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -3186,6 +4392,24 @@
       <c r="M68" t="str">
         <v>MetLife Stadium</v>
       </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
+      <c r="S68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -3227,6 +4451,24 @@
       <c r="M69" t="str">
         <v>Lincoln Financial Field</v>
       </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
+      <c r="R69" t="str">
+        <v/>
+      </c>
+      <c r="S69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70">
@@ -3268,6 +4510,24 @@
       <c r="M70" t="str">
         <v>Hard Rock Stadium</v>
       </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
+      <c r="R70" t="str">
+        <v/>
+      </c>
+      <c r="S70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71">
@@ -3309,6 +4569,24 @@
       <c r="M71" t="str">
         <v>Mercedes-Benz Stadium</v>
       </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72">
@@ -3350,6 +4628,24 @@
       <c r="M72" t="str">
         <v>GEHA Field at Arrowhead Stadium</v>
       </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
+      <c r="R72" t="str">
+        <v/>
+      </c>
+      <c r="S72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73">
@@ -3391,6 +4687,24 @@
       <c r="M73" t="str">
         <v>AT&amp;T Stadium</v>
       </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
+      <c r="R73" t="str">
+        <v/>
+      </c>
+      <c r="S73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74">
@@ -3432,6 +4746,24 @@
       <c r="M74" t="str">
         <v>SoFi Stadium</v>
       </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
+      <c r="S74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75">
@@ -3473,6 +4805,24 @@
       <c r="M75" t="str">
         <v>NRG Stadium</v>
       </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75" t="str">
+        <v/>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
+      <c r="S75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76">
@@ -3514,6 +4864,24 @@
       <c r="M76" t="str">
         <v>Gillette Stadium</v>
       </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
+        <v/>
+      </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
+      <c r="S76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77">
@@ -3555,6 +4923,24 @@
       <c r="M77" t="str">
         <v>Estadio BBVA</v>
       </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
+        <v/>
+      </c>
+      <c r="R77" t="str">
+        <v/>
+      </c>
+      <c r="S77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78">
@@ -3596,6 +4982,24 @@
       <c r="M78" t="str">
         <v>AT&amp;T Stadium</v>
       </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v/>
+      </c>
+      <c r="R78" t="str">
+        <v/>
+      </c>
+      <c r="S78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79">
@@ -3637,6 +5041,24 @@
       <c r="M79" t="str">
         <v>MetLife Stadium</v>
       </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v/>
+      </c>
+      <c r="R79" t="str">
+        <v/>
+      </c>
+      <c r="S79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80">
@@ -3678,6 +5100,24 @@
       <c r="M80" t="str">
         <v>Estadio Azteca</v>
       </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v/>
+      </c>
+      <c r="R80" t="str">
+        <v/>
+      </c>
+      <c r="S80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81">
@@ -3719,6 +5159,24 @@
       <c r="M81" t="str">
         <v>Mercedes-Benz Stadium</v>
       </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
+      <c r="R81" t="str">
+        <v/>
+      </c>
+      <c r="S81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82">
@@ -3760,6 +5218,24 @@
       <c r="M82" t="str">
         <v>Lumen Field</v>
       </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v/>
+      </c>
+      <c r="R82" t="str">
+        <v/>
+      </c>
+      <c r="S82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83">
@@ -3801,6 +5277,24 @@
       <c r="M83" t="str">
         <v>Levi's Stadium</v>
       </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
+      <c r="R83" t="str">
+        <v/>
+      </c>
+      <c r="S83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84">
@@ -3842,6 +5336,24 @@
       <c r="M84" t="str">
         <v>SoFi Stadium</v>
       </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
+      <c r="R84" t="str">
+        <v/>
+      </c>
+      <c r="S84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85">
@@ -3883,6 +5395,24 @@
       <c r="M85" t="str">
         <v>BMO Field</v>
       </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
+      <c r="R85" t="str">
+        <v/>
+      </c>
+      <c r="S85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86">
@@ -3924,6 +5454,24 @@
       <c r="M86" t="str">
         <v>BC Place</v>
       </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
+      <c r="R86" t="str">
+        <v/>
+      </c>
+      <c r="S86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87">
@@ -3965,6 +5513,24 @@
       <c r="M87" t="str">
         <v>AT&amp;T Stadium</v>
       </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
+      <c r="R87" t="str">
+        <v/>
+      </c>
+      <c r="S87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88">
@@ -4006,6 +5572,24 @@
       <c r="M88" t="str">
         <v>Hard Rock Stadium</v>
       </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
+      <c r="R88" t="str">
+        <v/>
+      </c>
+      <c r="S88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89">
@@ -4047,6 +5631,24 @@
       <c r="M89" t="str">
         <v>GEHA Field at Arrowhead Stadium</v>
       </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
+      <c r="R89" t="str">
+        <v/>
+      </c>
+      <c r="S89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90">
@@ -4088,6 +5690,24 @@
       <c r="M90" t="str">
         <v>NRG Stadium</v>
       </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
+      <c r="R90" t="str">
+        <v/>
+      </c>
+      <c r="S90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91">
@@ -4129,6 +5749,24 @@
       <c r="M91" t="str">
         <v>Lincoln Financial Field</v>
       </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+      <c r="R91" t="str">
+        <v/>
+      </c>
+      <c r="S91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92">
@@ -4170,6 +5808,24 @@
       <c r="M92" t="str">
         <v>MetLife Stadium</v>
       </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
+      <c r="R92" t="str">
+        <v/>
+      </c>
+      <c r="S92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93">
@@ -4211,6 +5867,24 @@
       <c r="M93" t="str">
         <v>Estadio Azteca</v>
       </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
+      <c r="R93" t="str">
+        <v/>
+      </c>
+      <c r="S93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94">
@@ -4252,6 +5926,24 @@
       <c r="M94" t="str">
         <v>AT&amp;T Stadium</v>
       </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
+      <c r="R94" t="str">
+        <v/>
+      </c>
+      <c r="S94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95">
@@ -4293,6 +5985,24 @@
       <c r="M95" t="str">
         <v>Lumen Field</v>
       </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v/>
+      </c>
+      <c r="R95" t="str">
+        <v/>
+      </c>
+      <c r="S95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96">
@@ -4334,6 +6044,24 @@
       <c r="M96" t="str">
         <v>Mercedes-Benz Stadium</v>
       </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v/>
+      </c>
+      <c r="R96" t="str">
+        <v/>
+      </c>
+      <c r="S96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97">
@@ -4375,6 +6103,24 @@
       <c r="M97" t="str">
         <v>BC Place</v>
       </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
+      <c r="R97" t="str">
+        <v/>
+      </c>
+      <c r="S97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -4416,6 +6162,24 @@
       <c r="M98" t="str">
         <v>Gillette Stadium</v>
       </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
+      <c r="R98" t="str">
+        <v/>
+      </c>
+      <c r="S98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -4457,6 +6221,24 @@
       <c r="M99" t="str">
         <v>SoFi Stadium</v>
       </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
+      <c r="R99" t="str">
+        <v/>
+      </c>
+      <c r="S99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100">
@@ -4498,6 +6280,24 @@
       <c r="M100" t="str">
         <v>Hard Rock Stadium</v>
       </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
+      <c r="R100" t="str">
+        <v/>
+      </c>
+      <c r="S100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -4539,6 +6339,24 @@
       <c r="M101" t="str">
         <v>GEHA Field at Arrowhead Stadium</v>
       </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
+      <c r="R101" t="str">
+        <v/>
+      </c>
+      <c r="S101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102">
@@ -4580,6 +6398,24 @@
       <c r="M102" t="str">
         <v>AT&amp;T Stadium</v>
       </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
+      <c r="R102" t="str">
+        <v/>
+      </c>
+      <c r="S102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103">
@@ -4621,6 +6457,24 @@
       <c r="M103" t="str">
         <v>Mercedes-Benz Stadium</v>
       </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+      <c r="S103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104">
@@ -4662,6 +6516,24 @@
       <c r="M104" t="str">
         <v>Hard Rock Stadium</v>
       </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+      <c r="S104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105">
@@ -4703,10 +6575,28 @@
       <c r="M105" t="str">
         <v>MetLife Stadium</v>
       </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
+      <c r="R105" t="str">
+        <v/>
+      </c>
+      <c r="S105" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M105"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S105"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend-excel/data/matches.xlsx
+++ b/backend-excel/data/matches.xlsx
@@ -602,13 +602,13 @@
         <v>🇧🇦</v>
       </c>
       <c r="I4" t="str">
-        <v>scheduled</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
+        <v>completed</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -616,11 +616,11 @@
       <c r="M4" t="str">
         <v>BMO Field</v>
       </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
       </c>
       <c r="P4" t="str">
         <v/>
@@ -661,13 +661,13 @@
         <v>🇵🇾</v>
       </c>
       <c r="I5" t="str">
-        <v>scheduled</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
+        <v>completed</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -675,11 +675,11 @@
       <c r="M5" t="str">
         <v>SoFi Stadium</v>
       </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
+      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
       </c>
       <c r="P5" t="str">
         <v/>
